--- a/LID_per_sub.xlsx
+++ b/LID_per_sub.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://myuva-my.sharepoint.com/personal/wnt6gp_virginia_edu/Documents/StreamLit/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\savan\Downloads\coastwise-main (1)\coastwise-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="18" documentId="13_ncr:1_{1852C1EA-C39D-4C6D-B25B-A0AA6EB64147}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F42CA0E6-0C1C-4A87-8962-D1A45EB9583A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE047180-A790-4EBD-9CAB-5C1B7CB5D4CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97454CBC-327E-48EE-B8D6-214EE2D65EB7}"/>
+    <workbookView xWindow="-28920" yWindow="-105" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{97454CBC-327E-48EE-B8D6-214EE2D65EB7}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabulat_Subcatc2" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Tabulat_Subcatc2!$A$1:$X$1</definedName>
   </definedNames>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>NAME</t>
   </si>
@@ -235,13 +236,22 @@
   </si>
   <si>
     <t>MaxNumber_RG</t>
+  </si>
+  <si>
+    <t>Number_Buildings</t>
+  </si>
+  <si>
+    <t>RG_1m_Cell</t>
+  </si>
+  <si>
+    <t>NumberRG</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -263,16 +273,33 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6E6E6"/>
+        <bgColor rgb="FFE6E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -280,11 +307,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -296,9 +335,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="STYLE0" xfId="1" xr:uid="{15BF8462-A943-46CE-87FC-66E08CEC1619}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4451,455 +4497,980 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF97A8AB-3850-455D-BD38-E44BBB953C1C}">
-  <dimension ref="A1:C40"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.85546875" style="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.7109375" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" style="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="11" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
+      <c r="D1" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="7">
-        <v>60.744334357333329</v>
-      </c>
-      <c r="C2" s="7">
-        <v>15.26753051136</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" t="s">
+      <c r="B2" s="9">
+        <f t="shared" ref="B2:B40" si="0">D2*2</f>
+        <v>28</v>
+      </c>
+      <c r="C2" s="10">
+        <v>13.088915046400002</v>
+      </c>
+      <c r="D2" s="9">
+        <v>14</v>
+      </c>
+      <c r="E2">
+        <v>1216</v>
+      </c>
+      <c r="F2" s="10">
+        <f>E2*10.7639104/1000</f>
+        <v>13.088915046400002</v>
+      </c>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C3" s="10">
+        <v>1.0225714880000001</v>
+      </c>
+      <c r="D3" s="9">
+        <v>15</v>
+      </c>
+      <c r="E3">
+        <v>95</v>
+      </c>
+      <c r="F3" s="10">
+        <f t="shared" ref="F3:F33" si="1">E3*10.7639104/1000</f>
+        <v>1.0225714880000001</v>
+      </c>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C4" s="10">
+        <v>5.6618168704</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>526</v>
+      </c>
+      <c r="F4" s="10">
+        <f t="shared" si="1"/>
+        <v>5.6618168704</v>
+      </c>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="9">
+        <f t="shared" si="0"/>
+        <v>52</v>
+      </c>
+      <c r="C5" s="10">
+        <v>67.123745254399992</v>
+      </c>
+      <c r="D5" s="9">
+        <v>26</v>
+      </c>
+      <c r="E5">
+        <v>6236</v>
+      </c>
+      <c r="F5" s="10">
+        <f t="shared" si="1"/>
+        <v>67.123745254399992</v>
+      </c>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="9">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+      <c r="C6" s="10">
+        <v>40.020218867200008</v>
+      </c>
+      <c r="D6" s="9">
+        <v>27</v>
+      </c>
+      <c r="E6">
+        <v>3718</v>
+      </c>
+      <c r="F6" s="10">
+        <f t="shared" si="1"/>
+        <v>40.020218867200008</v>
+      </c>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="9">
+        <f t="shared" si="0"/>
+        <v>164</v>
+      </c>
+      <c r="C7" s="10">
+        <v>168.05693307520002</v>
+      </c>
+      <c r="D7" s="9">
+        <v>82</v>
+      </c>
+      <c r="E7">
+        <v>15613</v>
+      </c>
+      <c r="F7" s="10">
+        <f t="shared" si="1"/>
+        <v>168.05693307520002</v>
+      </c>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C8" s="10">
+        <v>42.78654384</v>
+      </c>
+      <c r="D8" s="9">
+        <v>25</v>
+      </c>
+      <c r="E8">
+        <v>3975</v>
+      </c>
+      <c r="F8" s="10">
+        <f t="shared" si="1"/>
+        <v>42.78654384</v>
+      </c>
+      <c r="G8" s="10"/>
+      <c r="H8" s="10"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="9">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C9" s="10">
+        <v>7.3194590720000008</v>
+      </c>
+      <c r="D9" s="9">
+        <v>7</v>
+      </c>
+      <c r="E9">
+        <v>680</v>
+      </c>
+      <c r="F9" s="10">
+        <f t="shared" si="1"/>
+        <v>7.3194590720000008</v>
+      </c>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="9">
+        <f t="shared" si="0"/>
+        <v>30</v>
+      </c>
+      <c r="C10" s="10">
+        <v>52.129618067200006</v>
+      </c>
+      <c r="D10" s="9">
+        <v>15</v>
+      </c>
+      <c r="E10">
+        <v>4843</v>
+      </c>
+      <c r="F10" s="10">
+        <f t="shared" si="1"/>
+        <v>52.129618067200006</v>
+      </c>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C11" s="10">
+        <v>8.0514049792000009</v>
+      </c>
+      <c r="D11" s="9">
+        <v>8</v>
+      </c>
+      <c r="E11">
+        <v>748</v>
+      </c>
+      <c r="F11" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0514049792000009</v>
+      </c>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="9">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C12" s="10">
+        <v>12.970512032</v>
+      </c>
+      <c r="D12" s="9">
+        <v>14</v>
+      </c>
+      <c r="E12">
+        <v>1205</v>
+      </c>
+      <c r="F12" s="10">
+        <f t="shared" si="1"/>
+        <v>12.970512032</v>
+      </c>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="7">
-        <v>140.97134653866667</v>
-      </c>
-      <c r="C3" s="7">
-        <v>15.37732239744</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
+      <c r="B13" s="9">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C13" s="10">
+        <v>18.9660101248</v>
+      </c>
+      <c r="D13" s="9">
+        <v>16</v>
+      </c>
+      <c r="E13">
+        <v>1762</v>
+      </c>
+      <c r="F13" s="10">
+        <f t="shared" si="1"/>
+        <v>18.9660101248</v>
+      </c>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" s="9">
+        <f t="shared" si="0"/>
+        <v>136</v>
+      </c>
+      <c r="C14" s="10">
+        <v>139.50027878399999</v>
+      </c>
+      <c r="D14" s="9">
+        <v>68</v>
+      </c>
+      <c r="E14">
+        <v>12960</v>
+      </c>
+      <c r="F14" s="10">
+        <f t="shared" si="1"/>
+        <v>139.50027878399999</v>
+      </c>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C15" s="10">
+        <v>9.5691163455999995</v>
+      </c>
+      <c r="D15" s="9">
+        <v>9</v>
+      </c>
+      <c r="E15">
+        <v>889</v>
+      </c>
+      <c r="F15" s="10">
+        <f t="shared" si="1"/>
+        <v>9.5691163455999995</v>
+      </c>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B16" s="9">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C16" s="10">
+        <v>1.1517384128000001</v>
+      </c>
+      <c r="D16" s="9">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>107</v>
+      </c>
+      <c r="F16" s="10">
+        <f t="shared" si="1"/>
+        <v>1.1517384128000001</v>
+      </c>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" s="9">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C17" s="10">
+        <v>9.3861298688000012</v>
+      </c>
+      <c r="D17" s="9">
         <v>7</v>
       </c>
-      <c r="B4" s="7">
-        <v>41.333415936000002</v>
-      </c>
-      <c r="C4" s="7">
-        <v>10.053492313600001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+      <c r="E17">
+        <v>872</v>
+      </c>
+      <c r="F17" s="10">
+        <f t="shared" si="1"/>
+        <v>9.3861298688000012</v>
+      </c>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="9">
+        <f t="shared" si="0"/>
+        <v>50</v>
+      </c>
+      <c r="C18" s="10">
+        <v>50.116766822400002</v>
+      </c>
+      <c r="D18" s="9">
+        <v>25</v>
+      </c>
+      <c r="E18">
+        <v>4656</v>
+      </c>
+      <c r="F18" s="10">
+        <f t="shared" si="1"/>
+        <v>50.116766822400002</v>
+      </c>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="9">
+        <f t="shared" si="0"/>
+        <v>32</v>
+      </c>
+      <c r="C19" s="10">
+        <v>10.4732848192</v>
+      </c>
+      <c r="D19" s="9">
+        <v>16</v>
+      </c>
+      <c r="E19">
+        <v>973</v>
+      </c>
+      <c r="F19" s="10">
+        <f t="shared" si="1"/>
+        <v>10.4732848192</v>
+      </c>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="9">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="C20" s="10">
+        <v>18.847607110399998</v>
+      </c>
+      <c r="D20" s="9">
+        <v>35</v>
+      </c>
+      <c r="E20">
+        <v>1751</v>
+      </c>
+      <c r="F20" s="10">
+        <f t="shared" si="1"/>
+        <v>18.847607110399998</v>
+      </c>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="9">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C21" s="10">
+        <v>8.0514049792000009</v>
+      </c>
+      <c r="D21" s="9">
+        <v>17</v>
+      </c>
+      <c r="E21">
+        <v>748</v>
+      </c>
+      <c r="F21" s="10">
+        <f t="shared" si="1"/>
+        <v>8.0514049792000009</v>
+      </c>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="B22" s="9">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
+      <c r="C22" s="10">
+        <v>52.893855705599996</v>
+      </c>
+      <c r="D22" s="9">
+        <v>59</v>
+      </c>
+      <c r="E22">
+        <v>4914</v>
+      </c>
+      <c r="F22" s="10">
+        <f t="shared" si="1"/>
+        <v>52.893855705599996</v>
+      </c>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="9">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C23" s="10">
+        <v>24.918452576</v>
+      </c>
+      <c r="D23" s="9">
+        <v>24</v>
+      </c>
+      <c r="E23">
+        <v>2315</v>
+      </c>
+      <c r="F23" s="10">
+        <f t="shared" si="1"/>
+        <v>24.918452576</v>
+      </c>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="B24" s="9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="C24" s="10">
+        <v>3.552090432</v>
+      </c>
+      <c r="D24" s="9">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>330</v>
+      </c>
+      <c r="F24" s="10">
+        <f t="shared" si="1"/>
+        <v>3.552090432</v>
+      </c>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="9">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C25" s="10">
+        <v>7.6854320255999999</v>
+      </c>
+      <c r="D25" s="9">
+        <v>17</v>
+      </c>
+      <c r="E25">
+        <v>714</v>
+      </c>
+      <c r="F25" s="10">
+        <f t="shared" si="1"/>
+        <v>7.6854320255999999</v>
+      </c>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" s="9">
+        <f t="shared" si="0"/>
+        <v>28</v>
+      </c>
+      <c r="C26" s="10">
+        <v>23.551435955200002</v>
+      </c>
+      <c r="D26" s="9">
+        <v>14</v>
+      </c>
+      <c r="E26">
+        <v>2188</v>
+      </c>
+      <c r="F26" s="10">
+        <f t="shared" si="1"/>
+        <v>23.551435955200002</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="9">
+        <f t="shared" si="0"/>
+        <v>74</v>
+      </c>
+      <c r="C27" s="10">
+        <v>29.708392704000001</v>
+      </c>
+      <c r="D27" s="9">
+        <v>37</v>
+      </c>
+      <c r="E27">
+        <v>2760</v>
+      </c>
+      <c r="F27" s="10">
+        <f t="shared" si="1"/>
+        <v>29.708392704000001</v>
+      </c>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" s="9">
+        <f t="shared" si="0"/>
+        <v>48</v>
+      </c>
+      <c r="C28" s="10">
+        <v>12.6798864512</v>
+      </c>
+      <c r="D28" s="9">
+        <v>24</v>
+      </c>
+      <c r="E28">
+        <v>1178</v>
+      </c>
+      <c r="F28" s="10">
+        <f t="shared" si="1"/>
+        <v>12.6798864512</v>
+      </c>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="9">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C29" s="10">
+        <v>22.7226148544</v>
+      </c>
+      <c r="D29" s="9">
         <v>11</v>
       </c>
-      <c r="B5" s="7">
-        <v>75.777929216000004</v>
-      </c>
-      <c r="C5" s="7">
-        <v>3.0591033356800006</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
+      <c r="E29">
+        <v>2111</v>
+      </c>
+      <c r="F29" s="10">
+        <f t="shared" si="1"/>
+        <v>22.7226148544</v>
+      </c>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" s="9">
+        <f t="shared" si="0"/>
+        <v>24</v>
+      </c>
+      <c r="C30" s="10">
+        <v>23.4545607616</v>
+      </c>
+      <c r="D30" s="9">
+        <v>12</v>
+      </c>
+      <c r="E30">
+        <v>2179</v>
+      </c>
+      <c r="F30" s="10">
+        <f t="shared" si="1"/>
+        <v>23.4545607616</v>
+      </c>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="9">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+      <c r="C31" s="10">
+        <v>20.9465696384</v>
+      </c>
+      <c r="D31" s="9">
+        <v>7</v>
+      </c>
+      <c r="E31">
+        <v>1946</v>
+      </c>
+      <c r="F31" s="10">
+        <f t="shared" si="1"/>
+        <v>20.9465696384</v>
+      </c>
+      <c r="G31" s="10"/>
+      <c r="H31" s="10"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32" s="9">
+        <f t="shared" si="0"/>
+        <v>16</v>
+      </c>
+      <c r="C32" s="10">
+        <v>13.874680505600001</v>
+      </c>
+      <c r="D32" s="9">
+        <v>8</v>
+      </c>
+      <c r="E32">
+        <v>1289</v>
+      </c>
+      <c r="F32" s="10">
+        <f t="shared" si="1"/>
+        <v>13.874680505600001</v>
+      </c>
+      <c r="G32" s="10"/>
+      <c r="H32" s="10"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="9">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+      <c r="C33" s="10">
+        <v>27.813944473599999</v>
+      </c>
+      <c r="D33" s="9">
+        <v>19</v>
+      </c>
+      <c r="E33">
+        <v>2584</v>
+      </c>
+      <c r="F33" s="10">
+        <f t="shared" si="1"/>
+        <v>27.813944473599999</v>
+      </c>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B34" s="9">
+        <f t="shared" si="0"/>
+        <v>66</v>
+      </c>
+      <c r="C34" s="10">
+        <v>169.96214521600001</v>
+      </c>
+      <c r="D34" s="9">
+        <v>33</v>
+      </c>
+      <c r="E34">
+        <v>15790</v>
+      </c>
+      <c r="F34" s="10">
+        <f>E34*10.7639104/1000</f>
+        <v>169.96214521600001</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" s="9">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+      <c r="C35" s="10">
+        <v>5.8663311680000003</v>
+      </c>
+      <c r="D35" s="9">
+        <v>11</v>
+      </c>
+      <c r="E35">
+        <v>545</v>
+      </c>
+      <c r="F35" s="10">
+        <f t="shared" ref="F35:F40" si="2">E35*10.7639104/1000</f>
+        <v>5.8663311680000003</v>
+      </c>
+      <c r="G35" s="10"/>
+      <c r="H35" s="10"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
-        <v>46.715371136000002</v>
-      </c>
-      <c r="C6" s="7">
-        <v>3.6166738943999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
+      <c r="B36" s="9">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="C36" s="10">
+        <v>3.1000061952000002</v>
+      </c>
+      <c r="D36" s="9">
+        <v>5</v>
+      </c>
+      <c r="E36">
+        <v>288</v>
+      </c>
+      <c r="F36" s="10">
+        <f t="shared" si="2"/>
+        <v>3.1000061952000002</v>
+      </c>
+      <c r="G36" s="10"/>
+      <c r="H36" s="10"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="7">
-        <v>51.415612010666671</v>
-      </c>
-      <c r="C7" s="7">
-        <v>15.930587392000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
+      <c r="B37" s="9">
+        <f t="shared" si="0"/>
+        <v>18</v>
+      </c>
+      <c r="C37" s="10">
+        <v>8.9771012736000007</v>
+      </c>
+      <c r="D37" s="9">
+        <v>9</v>
+      </c>
+      <c r="E37">
+        <v>834</v>
+      </c>
+      <c r="F37" s="10">
+        <f t="shared" si="2"/>
+        <v>8.9771012736000007</v>
+      </c>
+      <c r="G37" s="10"/>
+      <c r="H37" s="10"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="7">
-        <v>1.1840301440000001</v>
-      </c>
-      <c r="C8" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
+      <c r="B38" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C38" s="10">
+        <v>5.1774409024000008</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38">
+        <v>481</v>
+      </c>
+      <c r="F38" s="10">
+        <f t="shared" si="2"/>
+        <v>5.1774409024000008</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="7">
-        <v>0</v>
-      </c>
-      <c r="C9" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
+      <c r="B39" s="9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C39" s="10">
+        <v>0.13993083519999999</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>13</v>
+      </c>
+      <c r="F39" s="10">
+        <f t="shared" si="2"/>
+        <v>0.13993083519999999</v>
+      </c>
+      <c r="G39" s="10"/>
+      <c r="H39" s="10"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="7">
-        <v>94.543013013333336</v>
-      </c>
-      <c r="C10" s="7">
-        <v>33.292774867200002</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="B11" s="7">
-        <v>123.42617258666668</v>
-      </c>
-      <c r="C11" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="7">
-        <v>8.0011733973333339</v>
-      </c>
-      <c r="C12" s="7">
-        <v>6.6305688064000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7">
-        <v>163.68319748266669</v>
-      </c>
-      <c r="C13" s="7">
-        <v>52.028437309440008</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="7">
-        <v>167.98876164266667</v>
-      </c>
-      <c r="C14" s="7">
-        <v>28.055056066560002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>10</v>
-      </c>
-      <c r="B15" s="7">
-        <v>480.393321152</v>
-      </c>
-      <c r="C15" s="7">
-        <v>259.08732332800002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>18</v>
-      </c>
-      <c r="B16" s="7">
-        <v>125.32779675733335</v>
-      </c>
-      <c r="C16" s="7">
-        <v>62.150818649600005</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="7">
-        <v>54.034830208000002</v>
-      </c>
-      <c r="C17" s="7">
-        <v>8.0341827225600007</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="B40" s="9">
+        <f t="shared" si="0"/>
+        <v>34</v>
+      </c>
+      <c r="C40" s="10">
+        <v>23.0132404352</v>
+      </c>
+      <c r="D40" s="9">
         <v>17</v>
       </c>
-      <c r="B18" s="7">
-        <v>91.780276010666668</v>
-      </c>
-      <c r="C18" s="7">
-        <v>52.947675257599997</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B19" s="7">
-        <v>92.139073023999998</v>
-      </c>
-      <c r="C19" s="7">
-        <v>3.4875069696000001</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="7">
-        <v>106.70623176533333</v>
-      </c>
-      <c r="C20" s="7">
-        <v>14.1437782656</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" s="7">
-        <v>361.34447212800001</v>
-      </c>
-      <c r="C21" s="7">
-        <v>122.05413280767999</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="7">
-        <v>103.15414133333333</v>
-      </c>
-      <c r="C22" s="7">
-        <v>3.2420898124800006</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23" s="7">
-        <v>11.768542037333333</v>
-      </c>
-      <c r="C23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" s="7">
-        <v>59.02210869333333</v>
-      </c>
-      <c r="C24" s="7">
-        <v>5.267857749760001</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>25</v>
-      </c>
-      <c r="B25" s="7">
-        <v>164.472550912</v>
-      </c>
-      <c r="C25" s="7">
-        <v>67.667322729600002</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="7">
-        <v>82.056876949333329</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B27" s="7">
-        <v>224.1763739306667</v>
-      </c>
-      <c r="C27" s="7">
-        <v>26.839810582400002</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="7">
-        <v>79.042982037333331</v>
-      </c>
-      <c r="C28" s="7">
-        <v>14.3805842944</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="7">
-        <v>359.26344945066666</v>
-      </c>
-      <c r="C29" s="7">
-        <v>65.659853440000006</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="7">
-        <v>163.826716288</v>
-      </c>
-      <c r="C30" s="7">
-        <v>16.867047596799999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="7">
-        <v>101.57543447466666</v>
-      </c>
-      <c r="C31" s="7">
-        <v>9.5971025126400011</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="7">
-        <v>89.448095424000002</v>
-      </c>
-      <c r="C32" s="7">
-        <v>36.037572019199999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="7">
-        <v>328.22750779733332</v>
-      </c>
-      <c r="C33" s="7">
-        <v>35.460626421759997</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>27</v>
-      </c>
-      <c r="B34" s="7">
-        <v>125.22015765333335</v>
-      </c>
-      <c r="C34" s="7">
-        <v>10.075020134399999</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="7">
-        <v>69.247823573333335</v>
-      </c>
-      <c r="C35" s="7">
-        <v>36.855629209600004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" t="s">
-        <v>32</v>
-      </c>
-      <c r="B36" s="7">
-        <v>77.069598463999995</v>
-      </c>
-      <c r="C36" s="7">
-        <v>35.8868772736</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="7">
-        <v>43.737355925333333</v>
-      </c>
-      <c r="C37" s="7">
-        <v>36.317433689600001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="7">
-        <v>62.645958528000001</v>
-      </c>
-      <c r="C38" s="7">
-        <v>17.825035622399998</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-      <c r="B39" s="7">
-        <v>106.09627684266667</v>
-      </c>
-      <c r="C39" s="7">
-        <v>30.440338611200001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>31</v>
-      </c>
-      <c r="B40" s="7">
-        <v>252.3778191786667</v>
-      </c>
-      <c r="C40" s="7">
-        <v>207.55833146111999</v>
-      </c>
+      <c r="E40">
+        <v>2138</v>
+      </c>
+      <c r="F40" s="10">
+        <f t="shared" si="2"/>
+        <v>23.0132404352</v>
+      </c>
+      <c r="G40" s="10"/>
+      <c r="H40" s="10"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B41" s="10"/>
+      <c r="C41" s="10"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:F1" xr:uid="{FF97A8AB-3850-455D-BD38-E44BBB953C1C}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>